--- a/tests/reports/selenium_test_report.xlsx
+++ b/tests/reports/selenium_test_report.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="J149" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="J175" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="J177" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="J185" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="J191" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="J193" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="J197" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="J199" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="J201" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="J205" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="J207" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="J211" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="J212" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="J221" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12512,7 +12512,7 @@
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="J223" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="J225" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="J229" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="J231" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="J233" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13765,7 +13765,7 @@
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="J247" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="J249" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="J251" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="J253" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14235,7 +14235,7 @@
       </c>
       <c r="J255" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="J257" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14445,7 +14445,7 @@
       </c>
       <c r="J259" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="J261" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="J263" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="J265" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="J267" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="J269" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="J271" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="J273" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="J275" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="J277" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15440,7 +15440,7 @@
       </c>
       <c r="J278" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="J279" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="J280" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15598,7 @@
       </c>
       <c r="J281" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="J282" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="J283" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="J284" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="J285" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="J286" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="J287" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="J288" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="J289" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="J290" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="J291" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="J292" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="J293" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="J294" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="J295" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="J296" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="J297" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="J298" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="J299" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="J300" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="J301" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 19:57:36</t>
+          <t>2026-07-23 20:08:48</t>
         </is>
       </c>
     </row>

--- a/tests/reports/selenium_test_report.xlsx
+++ b/tests/reports/selenium_test_report.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="J148" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="J149" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="J150" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="J151" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="J152" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="J154" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="J156" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="J158" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="J160" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="J162" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="J164" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J166" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="J168" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="J170" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="J172" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="J174" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="J175" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="J176" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="J177" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="J178" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="J180" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="J181" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="J182" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="J183" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="J184" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10573,7 +10573,7 @@
       </c>
       <c r="J185" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="J186" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="J188" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="J190" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="J191" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="J192" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="J193" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="J194" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="J196" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="J197" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="J198" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="J199" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="J200" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="J201" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="J202" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="J204" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="J205" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="J206" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="J207" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J208" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="J210" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="J211" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="J212" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="J214" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="J216" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="J218" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="J220" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="J221" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12512,7 +12512,7 @@
       </c>
       <c r="J222" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="J223" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="J224" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="J225" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="J226" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="J228" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="J229" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="J230" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="J231" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="J232" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="J233" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="J234" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="J236" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="J238" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="J240" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="J242" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="J244" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13765,7 +13765,7 @@
       </c>
       <c r="J246" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="J247" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="J248" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="J249" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="J250" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="J251" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="J252" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="J253" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="J254" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14235,7 +14235,7 @@
       </c>
       <c r="J255" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="J256" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="J257" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="J258" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14445,7 +14445,7 @@
       </c>
       <c r="J259" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="J260" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="J261" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="J262" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="J263" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="J264" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="J265" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="J266" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="J267" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="J268" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="J269" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="J270" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="J271" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="J272" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="J273" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="J274" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="J275" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="J276" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="J277" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15440,7 +15440,7 @@
       </c>
       <c r="J278" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="J279" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="J280" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15598,7 @@
       </c>
       <c r="J281" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="J282" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="J283" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="J284" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="J285" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="J286" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="J287" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -15962,7 +15962,7 @@
       </c>
       <c r="J288" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="J289" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="J290" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="J291" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="J292" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="J293" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="J294" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="J295" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="J296" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="J297" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="J298" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="J299" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="J300" s="14" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="J301" s="16" t="inlineStr">
         <is>
-          <t>2026-07-23 20:08:48</t>
+          <t>2026-07-24 08:34:59</t>
         </is>
       </c>
     </row>
